--- a/基本設計/01_システム全体基本設計書.xlsx
+++ b/基本設計/01_システム全体基本設計書.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rd95f416e56ec4289"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R15bb2c153b7a4f64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_システム概要" sheetId="6" r:id="R8c78476a12644258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_業務範囲" sheetId="7" r:id="R3453648faa04425d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_システム構成" sheetId="8" r:id="Re73a27a35de441b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_モジュール一覧" sheetId="9" r:id="R3e99cfb6fcca4ab2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re50bfa92947d4be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R7b5afa9c1cef49ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_システム概要" sheetId="6" r:id="R1ed9d180339d4834"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_業務範囲" sheetId="7" r:id="Re6cdd0555d494206"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_システム構成" sheetId="8" r:id="R78f89aa7c7fc47ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_モジュール一覧" sheetId="9" r:id="Rdf6b2d3e3e53443a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1239,10 +1239,7 @@
       <x:c r="F16" s="172"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1257,25 +1254,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="215" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="215"/>
-      <x:c r="D19" s="215"/>
-      <x:c r="E19" s="215"/>
-      <x:c r="F19" s="215"/>
-      <x:c r="G19" s="215"/>
-      <x:c r="H19" s="215"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="215"/>
-      <x:c r="C20" s="215"/>
-      <x:c r="D20" s="215"/>
-      <x:c r="E20" s="215"/>
-      <x:c r="F20" s="215"/>
-      <x:c r="G20" s="215"/>
-      <x:c r="H20" s="215"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="215"/>

--- a/基本設計/01_システム全体基本設計書.xlsx
+++ b/基本設計/01_システム全体基本設計書.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re50bfa92947d4be1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R7b5afa9c1cef49ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_システム概要" sheetId="6" r:id="R1ed9d180339d4834"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_業務範囲" sheetId="7" r:id="Re6cdd0555d494206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_システム構成" sheetId="8" r:id="R78f89aa7c7fc47ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_モジュール一覧" sheetId="9" r:id="Rdf6b2d3e3e53443a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rec99f0b666df4bd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rb0aaa18306fc439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_システム概要" sheetId="6" r:id="R78543dd18de14a3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_業務範囲" sheetId="7" r:id="Re59f4eaff1964553"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_システム構成" sheetId="8" r:id="R46ca4ddcdca24c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_モジュール一覧" sheetId="9" r:id="R16b121a2d2234570"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -362,7 +362,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="216">
+  <x:cellXfs count="233">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -811,6 +811,55 @@
     <x:xf numFmtId="0" fontId="23" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1179,8 +1228,8 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="216" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1189,8 +1238,8 @@
       <x:c r="H11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="210" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="C12" s="218" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="172" t="str">
         <x:v>CW-BD-SYS</x:v>
@@ -1202,8 +1251,8 @@
       <x:c r="C13" s="210" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="172" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="219" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="172"/>
       <x:c r="F13" s="172"/>
@@ -1212,8 +1261,8 @@
       <x:c r="C14" s="210" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="172" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="219" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="172"/>
       <x:c r="F14" s="172"/>
@@ -1232,23 +1281,29 @@
       <x:c r="C16" s="210" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="172" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="219" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="172"/>
       <x:c r="F16" s="172"/>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="221"/>
+      <x:c r="B17" s="221"/>
+      <x:c r="C17" s="221"/>
+      <x:c r="D17" s="221"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="221"/>
+      <x:c r="B18" s="221"/>
+      <x:c r="C18" s="221" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="221" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1356,41 +1411,29 @@
       <x:c r="G2" s="153"/>
       <x:c r="H2" s="153"/>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="155" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="140" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="140"/>
-      <x:c r="D3" s="155" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="140" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="140"/>
-      <x:c r="G3" s="140"/>
-      <x:c r="H3" s="140"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="155" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="140" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="140"/>
-      <x:c r="D4" s="155" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="140" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="140"/>
-      <x:c r="G4" s="140"/>
-      <x:c r="H4" s="140"/>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="224" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="63"/>
+      <x:c r="C3" s="63"/>
+      <x:c r="D3" s="224"/>
+      <x:c r="E3" s="63"/>
+      <x:c r="F3" s="63"/>
+      <x:c r="G3" s="63"/>
+      <x:c r="H3" s="63"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="224" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
+      <x:c r="C4" s="63"/>
+      <x:c r="D4" s="224"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="63"/>
+      <x:c r="G4" s="63"/>
+      <x:c r="H4" s="63"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1422,7 +1465,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="162" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="162" t="str">
         <x:v>作成者</x:v>
@@ -1460,7 +1503,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>基本設計初版</x:v>
@@ -1486,7 +1529,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>Leader Review後Baseline化</x:v>
@@ -1512,7 +1555,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>再監査指摘対応</x:v>
@@ -1538,7 +1581,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>再監査第2回指摘対応</x:v>
@@ -1563,8 +1606,8 @@
       <x:c r="F12" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G12" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G12" s="216" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" t="str">
         <x:v>再監査残項対応</x:v>
@@ -1589,8 +1632,8 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="216" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再Review指摘対応</x:v>
@@ -1615,25 +1658,127 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="216" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>従業員・部門業務仕様Review：用語・対象範囲を現行状態遷移へ統一</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G15" s="216" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>第2回業務仕様Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="110" customHeight="1">
+      <x:c r="A16" s="217" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B16" s="217" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C16" s="217" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D16" s="217" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" s="217" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" s="217" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" s="217" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H16" s="217" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="40" customHeight="1">
+      <x:c r="A17" s="217" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B17" s="217" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C17" s="217" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D17" s="217" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" s="217" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F17" s="217" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G17" s="217" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H17" s="217" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I17" s="217"/>
+      <x:c r="J17" s="217"/>
+      <x:c r="K17" s="217"/>
+      <x:c r="L17" s="217"/>
+    </x:row>
+    <x:row r="18" ht="100" customHeight="1">
+      <x:c r="A18" s="221" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B18" s="221" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C18" s="221" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D18" s="221" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E18" s="221" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F18" s="221" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G18" s="221" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H18" s="221" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1675,30 +1820,26 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="222" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="10"/>
-      <x:c r="G3" t="str">
-        <x:v>CW-BD-010</x:v>
-      </x:c>
+      <x:c r="G3" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="23" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C4" s="223" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="35" t="str">
         <x:v>作成日</x:v>
       </x:c>
       <x:c r="F4" s="37"/>
-      <x:c r="G4" s="36" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="G4" s="36" t="n"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="26" t="str">
@@ -1899,30 +2040,26 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="222" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="10"/>
-      <x:c r="G3" t="str">
-        <x:v>CW-BD-011</x:v>
-      </x:c>
+      <x:c r="G3" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="23" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C4" s="223" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="35" t="str">
         <x:v>作成日</x:v>
       </x:c>
       <x:c r="F4" s="37"/>
-      <x:c r="G4" s="36" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="G4" s="36" t="n"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="26" t="str">
@@ -1992,7 +2129,7 @@
         <x:v>対象</x:v>
       </x:c>
       <x:c r="C10" s="33" t="str">
-        <x:v>M03 従業員管理：登録、変更、照会、無効化、入退社</x:v>
+        <x:v>M03 従業員管理：登録、一般情報変更、照会、退職、Excel入出力</x:v>
       </x:c>
       <x:c r="D10" s="33" t="str">
         <x:v>○</x:v>
@@ -2204,6 +2341,30 @@
       <x:c r="E22" s="33" t="str">
         <x:v>将来拡張候補</x:v>
       </x:c>
+    </x:row>
+    <x:row r="23" ht="54" customHeight="1">
+      <x:c r="A23" s="217" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B23" s="217" t="str">
+        <x:v>設計方針</x:v>
+      </x:c>
+      <x:c r="C23" s="217" t="str">
+        <x:v>一般社内管理・単一構成、既存機能に限定</x:v>
+      </x:c>
+      <x:c r="D23" s="217" t="str">
+        <x:v>○</x:v>
+      </x:c>
+      <x:c r="E23" s="217" t="str">
+        <x:v>日報統計独立Menu・銀行級HA/多拠点/追加認証基盤は対象外。決定は00／04、業務正本18。</x:v>
+      </x:c>
+      <x:c r="F23" s="217"/>
+      <x:c r="G23" s="217"/>
+      <x:c r="H23" s="217"/>
+      <x:c r="I23" s="217"/>
+      <x:c r="J23" s="217"/>
+      <x:c r="K23" s="217"/>
+      <x:c r="L23" s="217"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2256,32 +2417,24 @@
       <x:c r="A3" s="62" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="63" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="D3" s="63" t="str">
-        <x:v>CW-BD-012</x:v>
-      </x:c>
+      <x:c r="B3" s="63" t="str"/>
+      <x:c r="C3" s="224" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="D3" s="63" t="str"/>
       <x:c r="E3" s="63"/>
       <x:c r="F3" s="63"/>
       <x:c r="G3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="D4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
+      <x:c r="A4" s="224" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
+      <x:c r="C4" s="224" t="str">
+        <x:v>改訂日：2026-09-24</x:v>
+      </x:c>
+      <x:c r="D4" s="63"/>
       <x:c r="E4" s="63"/>
       <x:c r="F4" s="63"/>
       <x:c r="G4"/>
@@ -2381,7 +2534,7 @@
         <x:v>REST API</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
-        <x:v>担当単位で選択</x:v>
+        <x:v>Build単位で選択。画面単位の混在なし。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -2401,7 +2554,7 @@
         <x:v>REST API</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
-        <x:v>担当単位で選択</x:v>
+        <x:v>Build単位で選択。画面単位の混在なし。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
@@ -2573,7 +2726,7 @@
       <x:c r="F20" s="64"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="88" t="str">
+      <x:c r="A21" s="225" t="str">
         <x:v>FrontendはVue版とReact版で同一画面ID・API契約を使用する。業務Rule・権限・DB更新責任はBackendが持つ。</x:v>
       </x:c>
       <x:c r="B21" s="89"/>
@@ -2582,13 +2735,27 @@
       <x:c r="E21" s="89"/>
       <x:c r="F21" s="90"/>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="91"/>
-      <x:c r="B22" s="92"/>
-      <x:c r="C22" s="92"/>
-      <x:c r="D22" s="92"/>
-      <x:c r="E22" s="92"/>
-      <x:c r="F22" s="93"/>
+    <x:row r="22" ht="100" customHeight="1">
+      <x:c r="A22" s="229"/>
+      <x:c r="B22" s="230"/>
+      <x:c r="C22" s="230"/>
+      <x:c r="D22" s="230"/>
+      <x:c r="E22" s="230"/>
+      <x:c r="F22" s="231"/>
+    </x:row>
+    <x:row r="23" ht="100" customHeight="1">
+      <x:c r="A23" s="221" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B23" s="221" t="str">
+        <x:v>Frontend実装方式</x:v>
+      </x:c>
+      <x:c r="C23" s="221" t="str">
+        <x:v>Vue版とReact版は同一基本設計・同一API契約に基づく代替実装。同一Production Build内で画面単位に混在させない。現行開発ScheduleはReact版。</x:v>
+      </x:c>
+      <x:c r="D23" s="221"/>
+      <x:c r="E23" s="221"/>
+      <x:c r="F23" s="221"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2602,8 +2769,6 @@
     <x:mergeCell ref="E4:F4"/>
     <x:mergeCell ref="F4:G4"/>
     <x:mergeCell ref="A6:F6"/>
-    <x:mergeCell ref="A20:F21"/>
-    <x:mergeCell ref="A21:F22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2649,13 +2814,9 @@
       <x:c r="A3" s="62" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="63" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="63" t="str"/>
       <x:c r="C3" s="63"/>
-      <x:c r="D3" s="62" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
+      <x:c r="D3" s="62" t="str"/>
       <x:c r="E3" s="63" t="str">
         <x:v>CW-BD-013</x:v>
       </x:c>
@@ -2664,18 +2825,14 @@
       <x:c r="H3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="62" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="224" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
-      <x:c r="D4" s="62" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
+      <x:c r="D4" s="62" t="str"/>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="63"/>
       <x:c r="G4" s="63"/>
@@ -2782,7 +2939,7 @@
         <x:v>従業員管理</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
-        <x:v>登録・変更・照会・停止・入退社・Excel I/O</x:v>
+        <x:v>登録・一般情報変更・照会・退職・Excel I/O</x:v>
       </x:c>
       <x:c r="D10" s="67" t="str">
         <x:v>管理者/PM</x:v>
@@ -3010,7 +3167,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G19" s="67" t="str">
-        <x:v>BATCH-001～005</x:v>
+        <x:v>BATCH-001～006</x:v>
       </x:c>
       <x:c r="H19"/>
     </x:row>
